--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791ED779-7EE6-46F8-A3BE-350E5C1BF1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC5D616-0EC2-490F-8A85-0C6F7E08201E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="138">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1886,11 +1886,6 @@
     <t>Enter State</t>
   </si>
   <si>
-    <t>summary_clear_cityfield
-summary_clickon_checkout
-verify_summary_mandatoryfields_error</t>
-  </si>
-  <si>
     <t>Enter City</t>
   </si>
   <si>
@@ -2001,6 +1996,12 @@
 catalogue_clickon_submitbtn
 redemptioncart_clickon_checkoutbtn
 verify_summary_cartpoints</t>
+  </si>
+  <si>
+    <t>summary_clear_cityfield
+summary_clickon_checkout
+summary_clickon_checkout
+verify_summary_mandatoryfields_error</t>
   </si>
 </sst>
 </file>
@@ -2965,7 +2966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -3044,7 +3045,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
@@ -3053,7 +3054,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>68</v>
@@ -3076,264 +3077,240 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>109</v>
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J6" s="1"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>104</v>
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J7" s="1"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
       <c r="M9" s="8"/>
-      <c r="N9" s="8" t="s">
-        <v>112</v>
-      </c>
+      <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>102</v>
+        <v>17</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -3343,32 +3320,30 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="8"/>
-      <c r="N10" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="O10" s="8"/>
-      <c r="P10" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -3378,43 +3353,45 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="8" t="s">
-        <v>114</v>
+      <c r="N11" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="O11" s="8"/>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="2" t="s">
         <v>91</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>102</v>
+        <v>22</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="1" t="s">
@@ -3424,58 +3401,56 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="L13" s="1"/>
       <c r="M13" s="8"/>
-      <c r="N13" s="8" t="s">
-        <v>97</v>
-      </c>
+      <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>84</v>
+        <v>28</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -3485,57 +3460,49 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>95</v>
+      </c>
       <c r="O14" s="8"/>
       <c r="P14" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+    <row r="15" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q15" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3544,16 +3511,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -3563,30 +3530,32 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="O16" s="8"/>
       <c r="P16" s="1" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -3596,30 +3565,32 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="N17" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="O17" s="8"/>
       <c r="P17" s="1" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>126</v>
+        <v>24</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -3629,10 +3600,12 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
+      <c r="N18" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="O18" s="8"/>
       <c r="P18" s="1" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>5</v>
@@ -3643,16 +3616,16 @@
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -3660,9 +3633,12 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M19" s="8"/>
       <c r="N19" s="8" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="1" t="s">
@@ -3672,21 +3648,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -3695,66 +3671,76 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="8" t="s">
-        <v>130</v>
-      </c>
+      <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="1" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:17" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q21" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>134</v>
+        <v>30</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -3767,9 +3753,210 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="N25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="O25" s="8"/>
+      <c r="P25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q28" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC5D616-0EC2-490F-8A85-0C6F7E08201E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E64E734-3F90-4194-BF9D-CBAFECAA4D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -1938,11 +1938,6 @@
     <t>Redemption Summary</t>
   </si>
   <si>
-    <t>summary_clickon_checkout
-summary_clickon_declaration_acceptbtn
-verify_summary_otpverfy_title</t>
-  </si>
-  <si>
     <t>OTP Verification</t>
   </si>
   <si>
@@ -2002,6 +1997,12 @@
 summary_clickon_checkout
 summary_clickon_checkout
 verify_summary_mandatoryfields_error</t>
+  </si>
+  <si>
+    <t>summary_clickon_checkout
+summary_clickon_checkout
+summary_clickon_declaration_acceptbtn
+verify_summary_otpverfy_title</t>
   </si>
 </sst>
 </file>
@@ -3045,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
@@ -3054,7 +3055,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>68</v>
@@ -3268,7 +3269,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>40</v>
@@ -3301,7 +3302,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>41</v>
@@ -3334,7 +3335,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>42</v>
@@ -3369,7 +3370,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>43</v>
@@ -3406,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>44</v>
@@ -3441,7 +3442,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>45</v>
@@ -3476,7 +3477,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>46</v>
@@ -3511,7 +3512,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>47</v>
@@ -3546,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>48</v>
@@ -3555,7 +3556,7 @@
         <v>25</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -3581,7 +3582,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>49</v>
@@ -3616,7 +3617,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>50</v>
@@ -3653,7 +3654,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>51</v>
@@ -3686,7 +3687,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>52</v>
@@ -3731,7 +3732,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>53</v>
@@ -3764,7 +3765,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>54</v>
@@ -3792,12 +3793,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="58" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>55</v>
@@ -3806,7 +3807,7 @@
         <v>33</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -3819,7 +3820,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>5</v>
@@ -3830,7 +3831,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>56</v>
@@ -3839,7 +3840,7 @@
         <v>61</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -3849,7 +3850,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="N25" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O25" s="8"/>
       <c r="P25" s="1" t="s">
@@ -3864,7 +3865,7 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>57</v>
@@ -3873,7 +3874,7 @@
         <v>62</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -3883,12 +3884,12 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>5</v>
@@ -3899,7 +3900,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>58</v>
@@ -3908,7 +3909,7 @@
         <v>63</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -3921,7 +3922,7 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>5</v>
@@ -3932,7 +3933,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>59</v>
@@ -3941,7 +3942,7 @@
         <v>64</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E64E734-3F90-4194-BF9D-CBAFECAA4D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3FD99D-AE57-4E29-9002-A9E09F0C0168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -3083,7 +3083,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>34</v>
@@ -3098,23 +3098,22 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="O3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>35</v>
@@ -3129,23 +3128,22 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+      <c r="O4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>36</v>
@@ -3160,23 +3158,22 @@
       <c r="G5" s="1"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+      <c r="O5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>37</v>
@@ -3191,23 +3188,22 @@
       <c r="G6" s="1"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+      <c r="O6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>38</v>
@@ -3222,23 +3218,22 @@
       <c r="G7" s="1"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+      <c r="O7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>39</v>
@@ -3253,16 +3248,15 @@
       <c r="G8" s="1"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="O8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3FD99D-AE57-4E29-9002-A9E09F0C0168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFABBDDD-C6C9-4237-838F-6D350B032664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="135">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>2602000005</t>
-  </si>
-  <si>
-    <t>04_Redemptions</t>
   </si>
   <si>
     <t>RedemptionSummaryPageTest_01</t>
@@ -1727,25 +1724,6 @@
   </si>
   <si>
     <t>CATALOGUE_CARTPOINTS</t>
-  </si>
-  <si>
-    <t>openredemptionsmenu
-redhistory_clickon_fabbutton
-catalogue_enter_searchdata
-catalogue_clickon_keyboardsearchicon
-hidekeyboard
-catalogue_enter_qty
-hidekeyboard
-catalogue_get_rewardproductcode
-catalogue_get_rewardproductdesc
-catalogue_get_rewardproductpoints
-catalogue_get_rewardproductqty
-catalogue_get_cartpoints
-catalogue_get_tdspoints
-catalogue_get_tdspercentage
-catalogue_clickon_submitbtn
-redemptioncart_clickon_checkoutbtn
-verify_summary_cartpoints</t>
   </si>
   <si>
     <t>CATALOGUE_PRODUCTCODE</t>
@@ -1808,10 +1786,6 @@
   </si>
   <si>
     <t>NEW_BALANCE_POINTS</t>
-  </si>
-  <si>
-    <t>summary_clickon_checkout
-verify_summary_deliveryaddress_error</t>
   </si>
   <si>
     <t>true</t>
@@ -3005,34 +2979,34 @@
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="H1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="M1" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P1" s="6" t="s">
         <v>2</v>
@@ -3046,22 +3020,22 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -3071,7 +3045,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="1" t="s">
@@ -3083,16 +3057,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -3101,7 +3075,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="1" t="s">
@@ -3113,16 +3087,16 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -3131,7 +3105,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="1" t="s">
@@ -3143,16 +3117,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -3161,7 +3135,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1" t="s">
@@ -3173,16 +3147,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -3191,7 +3165,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1" t="s">
@@ -3203,16 +3177,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -3221,7 +3195,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
@@ -3233,16 +3207,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -3251,7 +3225,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
@@ -3263,16 +3237,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -3285,7 +3259,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>5</v>
@@ -3296,16 +3270,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -3317,7 +3291,7 @@
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
@@ -3329,16 +3303,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -3349,11 +3323,11 @@
       <c r="L11" s="1"/>
       <c r="M11" s="8"/>
       <c r="N11" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>5</v>
@@ -3364,33 +3338,33 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>5</v>
@@ -3401,22 +3375,22 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -3425,7 +3399,7 @@
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>5</v>
@@ -3436,16 +3410,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -3456,11 +3430,11 @@
       <c r="L14" s="1"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>5</v>
@@ -3471,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3491,11 +3465,11 @@
       <c r="L15" s="1"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>5</v>
@@ -3506,16 +3480,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -3526,11 +3500,11 @@
       <c r="L16" s="1"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>5</v>
@@ -3541,16 +3515,16 @@
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -3561,11 +3535,11 @@
       <c r="L17" s="1"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>5</v>
@@ -3576,16 +3550,16 @@
         <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -3596,11 +3570,11 @@
       <c r="L18" s="1"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>5</v>
@@ -3611,16 +3585,16 @@
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -3629,15 +3603,15 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>5</v>
@@ -3648,16 +3622,16 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -3670,7 +3644,7 @@
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>5</v>
@@ -3681,41 +3655,41 @@
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="H21" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q21" s="12" t="s">
         <v>5</v>
@@ -3726,16 +3700,16 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -3748,7 +3722,7 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>5</v>
@@ -3759,16 +3733,16 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -3781,7 +3755,7 @@
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>5</v>
@@ -3792,16 +3766,16 @@
         <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>137</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -3814,7 +3788,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>5</v>
@@ -3825,16 +3799,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -3844,11 +3818,11 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="N25" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O25" s="8"/>
       <c r="P25" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>5</v>
@@ -3859,16 +3833,16 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -3878,12 +3852,12 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>5</v>
@@ -3894,16 +3868,16 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -3916,7 +3890,7 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>5</v>
@@ -3927,16 +3901,16 @@
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -3949,7 +3923,7 @@
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>5</v>
@@ -3964,24 +3938,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFABACE3-3308-446A-B281-33AC2A41F819}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="74.08984375" style="9" customWidth="1"/>
     <col min="5" max="5" width="47.08984375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="40.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.08984375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="30.26953125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="20.81640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.90625" style="2"/>
+    <col min="6" max="6" width="15.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.90625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.08984375" style="2" customWidth="1"/>
+    <col min="10" max="12" width="40.6328125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.36328125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="32.36328125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="30.26953125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -3998,304 +3976,953 @@
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="232" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="1" t="s">
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8" t="s">
-        <v>89</v>
-      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="L10" s="1"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>90</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="1"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O11" s="8"/>
+      <c r="P11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="8"/>
+      <c r="P12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="O14" s="8"/>
+      <c r="P14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="O16" s="8"/>
+      <c r="P16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="O17" s="8"/>
+      <c r="P17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O18" s="8"/>
+      <c r="P18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O19" s="8"/>
+      <c r="P19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="N25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="O25" s="8"/>
+      <c r="P25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q28" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFABBDDD-C6C9-4237-838F-6D350B032664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15302EED-595F-4E50-A180-5DC6D89A6844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="136">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1977,6 +1977,9 @@
 summary_clickon_checkout
 summary_clickon_declaration_acceptbtn
 verify_summary_otpverfy_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -2941,7 +2944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -3510,7 +3513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -3545,7 +3548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
@@ -3580,7 +3583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
@@ -3617,7 +3620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
@@ -3650,7 +3653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>8</v>
       </c>
@@ -3695,7 +3698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
@@ -3728,7 +3731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -3761,7 +3764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
@@ -3794,7 +3797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
@@ -3863,7 +3866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>8</v>
       </c>
@@ -3896,7 +3899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
@@ -3927,6 +3930,9 @@
       </c>
       <c r="Q28" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15302EED-595F-4E50-A180-5DC6D89A6844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953F428F-BFBD-44F6-8D63-CA2C626CC1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="137">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1980,6 +1980,23 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>redemptioncart_clickon_cancelbtn
+catalogue_enter_searchdata
+catalogue_clickon_keyboardsearchicon
+hidekeyboard
+catalogue_enter_qty
+hidekeyboard
+catalogue_clickon_submitbtn
+redemptioncart_clickon_checkoutbtn
+summary_enter_deliveredaddress
+summary_enter_pincode
+summary_enter_district
+summary_enter_panno
+summary_clickon_checkout
+summary_clickon_checkout
+verify_summary_declarationtitle</t>
   </si>
 </sst>
 </file>
@@ -3653,7 +3670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" s="14" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>8</v>
       </c>
@@ -3667,7 +3684,7 @@
         <v>30</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>67</v>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953F428F-BFBD-44F6-8D63-CA2C626CC1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A872D12-25ED-45AD-B1D9-342B48246946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="137">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -2961,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -3538,13 +3538,13 @@
         <v>131</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>133</v>
+        <v>23</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -3555,7 +3555,7 @@
       <c r="L17" s="1"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="1" t="s">
@@ -3565,7 +3565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
@@ -3573,13 +3573,13 @@
         <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>99</v>
+        <v>22</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -3587,7 +3587,9 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="s">
         <v>94</v>
@@ -3600,7 +3602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
@@ -3608,13 +3610,13 @@
         <v>131</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -3622,100 +3624,96 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="8" t="s">
-        <v>94</v>
-      </c>
+      <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:18" s="14" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" s="14" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="C20" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q21" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
@@ -3723,13 +3721,13 @@
         <v>131</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>118</v>
+        <v>31</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -3742,13 +3740,13 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -3756,13 +3754,13 @@
         <v>131</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -3775,13 +3773,13 @@
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
@@ -3789,13 +3787,13 @@
         <v>131</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -3804,11 +3802,12 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
+      <c r="N24" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="O24" s="8"/>
       <c r="P24" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>5</v>
@@ -3822,13 +3821,13 @@
         <v>131</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -3837,18 +3836,19 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-      <c r="N25" s="8" t="s">
-        <v>123</v>
-      </c>
+      <c r="M25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="1" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
@@ -3856,13 +3856,13 @@
         <v>131</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>130</v>
+        <v>62</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -3871,19 +3871,17 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="8" t="s">
-        <v>125</v>
-      </c>
+      <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>8</v>
       </c>
@@ -3891,13 +3889,13 @@
         <v>131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -3910,45 +3908,12 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="58" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R28" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>135</v>
       </c>
     </row>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A872D12-25ED-45AD-B1D9-342B48246946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5579E0-6FE8-4676-ADB8-5651EF73E823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5579E0-6FE8-4676-ADB8-5651EF73E823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E73FDC-347A-41E7-8FC8-F82B8C57462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="138">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1997,6 +1997,10 @@
 summary_clickon_checkout
 summary_clickon_checkout
 verify_summary_declarationtitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary_clickon_cancelbtn
+</t>
   </si>
 </sst>
 </file>
@@ -4616,7 +4620,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E73FDC-347A-41E7-8FC8-F82B8C57462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E40D35-FE60-4C82-8790-11B0670189AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="139">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1999,8 +1999,10 @@
 verify_summary_declarationtitle</t>
   </si>
   <si>
-    <t xml:space="preserve">summary_clickon_cancelbtn
-</t>
+    <t>summary_clickon_cancelbtn</t>
+  </si>
+  <si>
+    <t>Reward Catalogue</t>
   </si>
 </sst>
 </file>
@@ -4606,7 +4608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
@@ -4633,7 +4635,7 @@
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="1" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/03_RedemptionSummaryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E40D35-FE60-4C82-8790-11B0670189AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A064D36-6971-4F31-A48C-2B339C8A3004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="137">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1997,12 +1997,6 @@
 summary_clickon_checkout
 summary_clickon_checkout
 verify_summary_declarationtitle</t>
-  </si>
-  <si>
-    <t>summary_clickon_cancelbtn</t>
-  </si>
-  <si>
-    <t>Reward Catalogue</t>
   </si>
 </sst>
 </file>
@@ -3932,7 +3926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFABACE3-3308-446A-B281-33AC2A41F819}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -4608,85 +4602,85 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:17" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="14" customFormat="1" ht="203" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="C20" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q21" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
@@ -4694,13 +4688,13 @@
         <v>131</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>118</v>
+        <v>31</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -4713,13 +4707,13 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -4727,13 +4721,13 @@
         <v>131</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -4746,13 +4740,13 @@
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
@@ -4760,13 +4754,13 @@
         <v>131</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -4775,11 +4769,12 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
+      <c r="N24" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="O24" s="8"/>
       <c r="P24" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>5</v>
@@ -4793,13 +4788,13 @@
         <v>131</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -4808,18 +4803,19 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-      <c r="N25" s="8" t="s">
-        <v>123</v>
-      </c>
+      <c r="M25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="1" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
@@ -4827,13 +4823,13 @@
         <v>131</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>130</v>
+        <v>62</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -4842,19 +4838,17 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="8" t="s">
-        <v>125</v>
-      </c>
+      <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>8</v>
       </c>
@@ -4862,13 +4856,13 @@
         <v>131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -4881,42 +4875,9 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="58" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q28" s="1" t="s">
         <v>5</v>
       </c>
     </row>
